--- a/curriculum-and-lore/Stonegrove_University_Curriculum_v7.xlsx
+++ b/curriculum-and-lore/Stonegrove_University_Curriculum_v7.xlsx
@@ -4063,7 +4063,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4_1_13</t>
+          <t>4_1_2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4123,7 +4123,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3_5_23</t>
+          <t>3_5_12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4243,7 +4243,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3_4_19</t>
+          <t>3_4_8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4363,7 +4363,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5_2_16</t>
+          <t>5_2_5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4423,7 +4423,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5_3_22</t>
+          <t>5_3_11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4483,7 +4483,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5_2_17</t>
+          <t>5_2_6</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4603,7 +4603,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3_4_14</t>
+          <t>3_4_6</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4783,7 +4783,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3_5_22</t>
+          <t>3_5_11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4843,7 +4843,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5_3_19</t>
+          <t>5_3_8</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4903,7 +4903,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3_5_24</t>
+          <t>3_5_13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5023,7 +5023,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4_1_12</t>
+          <t>4_1_1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5083,7 +5083,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5_3_23</t>
+          <t>5_3_12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5143,7 +5143,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3_5_20</t>
+          <t>3_5_9</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5203,7 +5203,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4_2_23</t>
+          <t>4_2_12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5443,7 +5443,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5_1_14</t>
+          <t>5_1_3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5503,7 +5503,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5_3_20</t>
+          <t>5_3_9</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5563,7 +5563,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>4_2_22</t>
+          <t>4_2_11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5623,7 +5623,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3_6_25</t>
+          <t>3_6_14</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5683,7 +5683,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5_1_12</t>
+          <t>5_1_2</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5863,7 +5863,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5_2_15</t>
+          <t>5_2_4</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5923,7 +5923,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4_2_15</t>
+          <t>4_2_4</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5983,7 +5983,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3_5_21</t>
+          <t>3_5_10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6043,7 +6043,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3_3_16</t>
+          <t>3_3_5</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -6223,7 +6223,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4_2_17</t>
+          <t>4_2_9</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -6343,7 +6343,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3_3_12</t>
+          <t>3_3_3</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6463,7 +6463,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4_2_16</t>
+          <t>4_2_5</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -6523,7 +6523,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>4_1_14</t>
+          <t>4_1_3</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6583,7 +6583,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4_2_21</t>
+          <t>4_2_10</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6643,7 +6643,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4_2_17</t>
+          <t>4_2_6</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6703,7 +6703,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>5_3_21</t>
+          <t>5_3_10</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6823,7 +6823,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4_2_19</t>
+          <t>4_2_8</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6883,7 +6883,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3_6_26</t>
+          <t>3_6_15</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -7120,7 +7120,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>4_2_18</t>
+          <t>4_2_7</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -7180,7 +7180,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5_3_18</t>
+          <t>5_3_7</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -7297,7 +7297,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>4_1_13</t>
+          <t>4_1_3</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -7354,7 +7354,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>5_2_13</t>
+          <t>5_2_5</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -7471,7 +7471,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4_2_19</t>
+          <t>4_2_10</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -7645,7 +7645,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3_4_17</t>
+          <t>3_4_7</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7759,7 +7759,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>5_2_13</t>
+          <t>5_2_4</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7816,7 +7816,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3_4_18</t>
+          <t>3_4_7</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7933,7 +7933,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3_5_20</t>
+          <t>3_5_12</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -8047,7 +8047,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>5_3_19</t>
+          <t>5_3_9</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -8161,7 +8161,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>5_1_11</t>
+          <t>5_1_3</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -8389,7 +8389,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5_2_12</t>
+          <t>5_2_4</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8446,7 +8446,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>4_2_16</t>
+          <t>4_2_8</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8503,7 +8503,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>5_3_21</t>
+          <t>5_3_11</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8560,7 +8560,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>4_2_22</t>
+          <t>4_2_12</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8617,7 +8617,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3_3_13</t>
+          <t>3_3_3</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8731,7 +8731,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>4_2_20</t>
+          <t>4_2_12</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8845,7 +8845,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>4_2_17</t>
+          <t>4_2_8</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8959,7 +8959,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>5_2_16</t>
+          <t>5_2_6</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -9016,7 +9016,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>4_2_13</t>
+          <t>4_2_5</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -9130,7 +9130,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>5_3_18</t>
+          <t>5_3_8</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9244,7 +9244,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>4_2_21</t>
+          <t>4_2_12</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9358,7 +9358,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>3_5_18</t>
+          <t>3_5_10</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9415,7 +9415,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>5_2_15</t>
+          <t>5_2_5</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9586,7 +9586,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>3_5_21</t>
+          <t>3_5_11</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9643,7 +9643,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>3_4_15</t>
+          <t>3_4_7</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9700,7 +9700,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>3_5_23</t>
+          <t>3_5_13</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9757,7 +9757,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>3_5_22</t>
+          <t>3_5_13</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9814,7 +9814,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>5_3_17</t>
+          <t>5_3_9</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9871,7 +9871,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>3_3_11</t>
+          <t>3_3_3</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9928,7 +9928,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>3_3_14</t>
+          <t>3_3_3</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9985,7 +9985,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>3_5_21</t>
+          <t>3_5_13</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10099,7 +10099,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>4_2_13</t>
+          <t>4_2_4</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10156,7 +10156,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>5_3_20</t>
+          <t>5_3_11</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10213,7 +10213,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>4_2_21</t>
+          <t>4_2_11</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10270,7 +10270,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>4_1_9</t>
+          <t>4_1_1</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10384,7 +10384,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>4_2_15</t>
+          <t>4_2_7</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10441,7 +10441,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>3_4_16</t>
+          <t>3_4_7</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10555,7 +10555,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>4_2_12</t>
+          <t>4_2_4</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10669,7 +10669,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>4_1_11</t>
+          <t>4_1_1</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10783,7 +10783,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>3_5_15</t>
+          <t>3_5_11</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10954,7 +10954,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>3_6_23</t>
+          <t>3_6_15</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11011,7 +11011,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>3_6_25</t>
+          <t>3_6_15</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11068,7 +11068,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>5_1_13</t>
+          <t>5_1_2</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11239,7 +11239,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>5_2_14</t>
+          <t>5_2_4</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11296,7 +11296,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>4_2_14</t>
+          <t>4_2_5</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11353,7 +11353,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>3_4_17</t>
+          <t>3_4_6</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11467,7 +11467,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>5_3_19</t>
+          <t>5_3_11</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11524,7 +11524,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>3_3_15</t>
+          <t>3_3_5</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11695,7 +11695,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>4_2_18</t>
+          <t>4_2_10</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11752,7 +11752,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>3_4_17</t>
+          <t>3_4_8</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11809,7 +11809,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>4_2_15</t>
+          <t>4_2_5</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11866,7 +11866,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>5_3_16</t>
+          <t>5_3_7</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11923,7 +11923,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>4_1_11</t>
+          <t>4_1_2</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11980,7 +11980,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>4_1_10</t>
+          <t>4_1_1</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12037,7 +12037,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>3_5_18</t>
+          <t>3_5_9</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12094,7 +12094,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>5_3_17</t>
+          <t>5_3_7</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12151,7 +12151,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>3_4_18</t>
+          <t>3_4_8</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12208,7 +12208,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>4_1_12</t>
+          <t>4_1_3</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12322,7 +12322,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>4_2_19</t>
+          <t>4_2_11</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12379,7 +12379,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>3_5_19</t>
+          <t>3_5_9</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12436,7 +12436,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>5_2_10</t>
+          <t>5_2_5</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12493,7 +12493,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>5_2_12</t>
+          <t>5_2_5</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12607,7 +12607,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>5_3_19</t>
+          <t>5_3_10</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12721,7 +12721,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>3_5_19</t>
+          <t>3_5_11</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12778,7 +12778,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>4_2_16</t>
+          <t>4_2_6</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12835,7 +12835,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>4_2_19</t>
+          <t>4_2_12</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12949,7 +12949,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>4_2_18</t>
+          <t>4_2_8</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13177,7 +13177,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>5_1_11</t>
+          <t>5_1_2</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13234,7 +13234,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>3_6_24</t>
+          <t>3_6_15</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13291,7 +13291,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>5_2_14</t>
+          <t>5_2_6</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13405,7 +13405,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>4_2_15</t>
+          <t>4_2_6</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13462,7 +13462,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>3_6_19</t>
+          <t>3_6_14</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13576,7 +13576,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>3_6_24</t>
+          <t>3_6_14</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13633,7 +13633,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>3_3_13</t>
+          <t>3_3_5</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13690,7 +13690,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>3_6_22</t>
+          <t>3_6_14</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13747,7 +13747,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>5_3_20</t>
+          <t>5_3_10</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13918,7 +13918,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>4_2_16</t>
+          <t>4_2_10</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13975,7 +13975,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>4_1_12</t>
+          <t>4_1_2</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14089,7 +14089,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>3_5_20</t>
+          <t>3_5_11</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14146,7 +14146,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>5_3_18</t>
+          <t>5_3_9</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14203,7 +14203,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>4_1_6</t>
+          <t>4_1_2</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14260,7 +14260,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>5_2_11</t>
+          <t>5_2_6</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14317,7 +14317,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>5_3_15</t>
+          <t>5_3_7</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14374,7 +14374,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>5_3_17</t>
+          <t>5_3_8</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14431,7 +14431,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>5_3_20</t>
+          <t>5_3_12</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14488,7 +14488,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>5_1_13</t>
+          <t>5_1_3</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14602,7 +14602,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>3_5_20</t>
+          <t>3_5_10</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14716,7 +14716,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>5_2_15</t>
+          <t>5_2_6</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14944,7 +14944,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>3_5_21</t>
+          <t>3_5_12</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15001,7 +15001,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>3_5_22</t>
+          <t>3_5_12</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15115,7 +15115,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>3_5_17</t>
+          <t>3_5_11</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15172,7 +15172,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>3_3_10</t>
+          <t>3_3_5</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15229,7 +15229,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>5_1_10</t>
+          <t>5_1_2</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15286,7 +15286,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>5_1_12</t>
+          <t>5_1_3</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15343,7 +15343,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>4_1_7</t>
+          <t>4_1_2</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15400,7 +15400,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>5_1_7</t>
+          <t>5_1_2</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15514,7 +15514,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>4_2_18</t>
+          <t>4_2_9</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15571,7 +15571,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>3_5_16</t>
+          <t>3_5_12</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15742,7 +15742,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>3_5_17</t>
+          <t>3_5_9</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15913,7 +15913,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>3_4_12</t>
+          <t>3_4_6</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -15970,7 +15970,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>4_2_14</t>
+          <t>4_2_6</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16027,7 +16027,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>3_3_9</t>
+          <t>3_3_5</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16198,7 +16198,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>5_3_18</t>
+          <t>5_3_10</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16255,7 +16255,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>4_2_19</t>
+          <t>4_2_9</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16312,7 +16312,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>3_5_19</t>
+          <t>3_5_10</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16369,7 +16369,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>4_2_14</t>
+          <t>4_2_4</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16597,7 +16597,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>3_3_14</t>
+          <t>3_3_5</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -16654,7 +16654,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>4_2_20</t>
+          <t>4_2_9</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -16711,7 +16711,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>3_6_23</t>
+          <t>3_6_14</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -16825,7 +16825,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>3_5_15</t>
+          <t>3_5_10</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -16882,7 +16882,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>3_4_16</t>
+          <t>3_4_8</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17110,7 +17110,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>4_2_16</t>
+          <t>4_2_7</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17224,7 +17224,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>5_3_22</t>
+          <t>5_3_12</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -17281,7 +17281,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>3_6_21</t>
+          <t>3_6_15</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -17338,7 +17338,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>3_5_18</t>
+          <t>3_5_13</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -17623,7 +17623,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>3_4_15</t>
+          <t>3_4_6</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -17680,7 +17680,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>4_1_10</t>
+          <t>4_1_2</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -17737,7 +17737,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>5_3_13</t>
+          <t>5_3_8</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -17908,7 +17908,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>3_5_16</t>
+          <t>3_5_9</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -17965,7 +17965,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>5_3_16</t>
+          <t>5_3_12</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -18022,7 +18022,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>5_2_9</t>
+          <t>5_2_4</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -18079,7 +18079,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>3_5_14</t>
+          <t>3_5_10</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -18136,7 +18136,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>5_3_17</t>
+          <t>5_3_12</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -18250,7 +18250,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>4_2_11</t>
+          <t>4_2_7</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -18421,7 +18421,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>5_2_11</t>
+          <t>5_2_4</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -18649,7 +18649,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>4_2_10</t>
+          <t>4_2_4</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -18706,7 +18706,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>3_5_15</t>
+          <t>3_5_9</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -18763,7 +18763,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>5_3_16</t>
+          <t>5_3_11</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -18820,7 +18820,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>5_2_14</t>
+          <t>5_2_5</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -18877,7 +18877,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>5_3_21</t>
+          <t>5_3_12</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -18991,7 +18991,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>4_2_18</t>
+          <t>4_2_12</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -19048,7 +19048,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>5_3_17</t>
+          <t>5_3_10</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -19105,7 +19105,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>3_4_14</t>
+          <t>3_4_8</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -19219,7 +19219,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>3_6_22</t>
+          <t>3_6_15</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -19390,7 +19390,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>3_4_16</t>
+          <t>3_4_6</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -19618,7 +19618,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>4_2_11</t>
+          <t>4_2_5</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -19903,7 +19903,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>3_3_10</t>
+          <t>3_3_3</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -20017,7 +20017,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>3_6_19</t>
+          <t>3_6_15</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -20131,7 +20131,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>4_1_5</t>
+          <t>4_1_1</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -20245,7 +20245,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>5_2_10</t>
+          <t>5_2_6</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -20359,7 +20359,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>3_5_14</t>
+          <t>3_5_9</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -20530,7 +20530,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>4_1_8</t>
+          <t>4_1_3</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -20587,7 +20587,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>4_2_11</t>
+          <t>4_2_4</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -20644,7 +20644,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>5_3_18</t>
+          <t>5_3_11</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -20701,7 +20701,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>4_2_17</t>
+          <t>4_2_7</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -20758,7 +20758,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>4_2_20</t>
+          <t>4_2_10</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -20815,7 +20815,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>5_3_16</t>
+          <t>5_3_8</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -20872,7 +20872,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>4_2_11</t>
+          <t>4_2_6</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -20986,7 +20986,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>4_2_20</t>
+          <t>4_2_11</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -21100,7 +21100,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>3_5_13</t>
+          <t>3_5_9</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -21271,7 +21271,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>3_5_19</t>
+          <t>3_5_13</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -21328,7 +21328,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>3_4_10</t>
+          <t>3_4_6</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -21385,7 +21385,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>3_4_13</t>
+          <t>3_4_8</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -21442,7 +21442,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>5_3_12</t>
+          <t>5_3_7</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -21499,7 +21499,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>4_2_10</t>
+          <t>4_2_5</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -21556,7 +21556,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>3_5_16</t>
+          <t>3_5_11</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -21670,7 +21670,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>5_3_12</t>
+          <t>5_3_8</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -21727,7 +21727,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>3_3_7</t>
+          <t>3_3_3</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -21841,7 +21841,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>5_3_16</t>
+          <t>5_3_9</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -21898,7 +21898,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>4_1_7</t>
+          <t>4_1_1</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -22012,7 +22012,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>4_1_11</t>
+          <t>4_1_3</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -22069,7 +22069,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>5_3_16</t>
+          <t>5_3_10</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -22126,7 +22126,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>3_6_20</t>
+          <t>3_6_14</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -22183,7 +22183,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>5_1_9</t>
+          <t>5_1_3</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -22240,7 +22240,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>4_2_16</t>
+          <t>4_2_11</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -22411,7 +22411,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>3_3_11</t>
+          <t>3_3_5</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -22468,7 +22468,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>4_2_18</t>
+          <t>4_2_11</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -22639,7 +22639,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>3_6_20</t>
+          <t>3_6_15</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -22810,7 +22810,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>5_2_8</t>
+          <t>5_2_4</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -22867,7 +22867,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>5_3_17</t>
+          <t>5_3_11</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -22981,7 +22981,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>5_3_14</t>
+          <t>5_3_8</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -23038,7 +23038,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>4_2_12</t>
+          <t>4_2_7</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -23152,7 +23152,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>4_2_10</t>
+          <t>4_2_6</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -23380,7 +23380,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>5_1_7</t>
+          <t>5_1_3</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -23551,7 +23551,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>4_2_17</t>
+          <t>4_2_12</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -23608,7 +23608,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>5_3_19</t>
+          <t>5_3_12</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -23665,7 +23665,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>5_3_14</t>
+          <t>5_3_9</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -23779,7 +23779,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>4_2_17</t>
+          <t>4_2_11</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -23893,7 +23893,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>4_1_8</t>
+          <t>4_1_1</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -24007,7 +24007,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>4_2_9</t>
+          <t>4_2_5</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -24121,7 +24121,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>3_5_16</t>
+          <t>3_5_10</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -24178,7 +24178,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>5_3_18</t>
+          <t>5_3_12</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -24235,7 +24235,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>5_2_11</t>
+          <t>5_2_5</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -24292,7 +24292,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>4_2_14</t>
+          <t>4_2_8</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -24349,7 +24349,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>3_5_18</t>
+          <t>3_5_11</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -24406,7 +24406,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>4_1_7</t>
+          <t>4_1_3</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -24463,7 +24463,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>5_1_6</t>
+          <t>5_1_2</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -24520,7 +24520,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>5_3_13</t>
+          <t>5_3_9</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -24577,7 +24577,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>5_3_15</t>
+          <t>5_3_10</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -24691,7 +24691,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>5_3_13</t>
+          <t>5_3_10</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -24748,7 +24748,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>3_5_18</t>
+          <t>3_5_12</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -24862,7 +24862,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>5_1_3</t>
+          <t>5_1_2</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -24919,7 +24919,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>5_3_15</t>
+          <t>5_3_11</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -24976,7 +24976,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>4_2_12</t>
+          <t>4_2_6</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -25090,7 +25090,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>5_3_15</t>
+          <t>5_3_9</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -25147,7 +25147,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>3_3_12</t>
+          <t>3_3_5</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -25204,7 +25204,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>4_2_13</t>
+          <t>4_2_7</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -25318,7 +25318,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>5_2_12</t>
+          <t>5_2_6</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -25375,7 +25375,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>5_1_10</t>
+          <t>5_1_3</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -25546,7 +25546,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>4_1_9</t>
+          <t>4_1_3</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -25660,7 +25660,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>3_5_12</t>
+          <t>3_5_11</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -25774,7 +25774,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>3_4_12</t>
+          <t>3_4_8</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -25831,7 +25831,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>3_3_8</t>
+          <t>3_3_3</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -25888,7 +25888,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>4_2_12</t>
+          <t>4_2_5</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -26002,7 +26002,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>5_2_10</t>
+          <t>5_2_4</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -26059,7 +26059,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>4_2_8</t>
+          <t>4_2_4</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -26173,7 +26173,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>4_2_6</t>
+          <t>4_2_5</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -26230,7 +26230,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>5_3_14</t>
+          <t>5_3_10</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -26344,7 +26344,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>4_1_9</t>
+          <t>4_1_2</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -26458,7 +26458,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>4_2_16</t>
+          <t>4_2_12</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -26515,7 +26515,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>4_1_5</t>
+          <t>4_1_3</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -26572,7 +26572,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>4_2_15</t>
+          <t>4_2_9</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -26629,7 +26629,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>4_2_14</t>
+          <t>4_2_12</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -26686,7 +26686,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>3_4_9</t>
+          <t>3_4_7</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -26800,7 +26800,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>4_2_13</t>
+          <t>4_2_9</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -26857,7 +26857,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>4_2_7</t>
+          <t>4_2_4</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -26914,7 +26914,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>3_5_13</t>
+          <t>3_5_11</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -27028,7 +27028,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>5_3_15</t>
+          <t>5_3_8</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -27085,7 +27085,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>3_4_12</t>
+          <t>3_4_7</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -27142,7 +27142,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>4_2_14</t>
+          <t>4_2_10</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -27199,7 +27199,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>4_2_15</t>
+          <t>4_2_11</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -27313,7 +27313,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>5_2_7</t>
+          <t>5_2_6</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -27598,7 +27598,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>4_2_15</t>
+          <t>4_2_8</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -27655,7 +27655,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>3_4_14</t>
+          <t>3_4_7</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -27712,7 +27712,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>5_1_8</t>
+          <t>5_1_3</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -27769,7 +27769,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>3_5_19</t>
+          <t>3_5_12</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -27826,7 +27826,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>4_1_10</t>
+          <t>4_1_3</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -27883,7 +27883,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>3_4_13</t>
+          <t>3_4_6</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -28054,7 +28054,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>3_4_11</t>
+          <t>3_4_7</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -28111,7 +28111,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>5_2_9</t>
+          <t>5_2_6</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -28282,7 +28282,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>4_2_13</t>
+          <t>4_2_6</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -28339,7 +28339,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>3_6_16</t>
+          <t>3_6_14</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -28453,7 +28453,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>3_6_18</t>
+          <t>3_6_14</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -28510,7 +28510,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>4_1_8</t>
+          <t>4_1_2</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -28567,7 +28567,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>5_3_11</t>
+          <t>5_3_7</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -28624,7 +28624,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>5_3_14</t>
+          <t>5_3_12</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -28681,7 +28681,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>5_3_8</t>
+          <t>5_3_7</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -28738,7 +28738,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>5_2_9</t>
+          <t>5_2_5</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -28795,7 +28795,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>3_4_11</t>
+          <t>3_4_6</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -28909,7 +28909,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>3_3_6</t>
+          <t>3_3_5</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -29023,7 +29023,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>4_2_9</t>
+          <t>4_2_6</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -29080,7 +29080,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>3_5_17</t>
+          <t>3_5_13</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -29194,7 +29194,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>3_4_9</t>
+          <t>3_4_6</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -29251,7 +29251,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>3_6_21</t>
+          <t>3_6_14</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -29365,7 +29365,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>5_1_9</t>
+          <t>5_1_2</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -29422,7 +29422,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>3_3_9</t>
+          <t>3_3_3</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -29479,7 +29479,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>3_5_10</t>
+          <t>3_5_9</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -29764,7 +29764,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>3_4_13</t>
+          <t>3_4_7</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -29878,7 +29878,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>3_5_16</t>
+          <t>3_5_13</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -29935,7 +29935,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>5_2_13</t>
+          <t>5_2_6</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -29992,7 +29992,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>5_1_4</t>
+          <t>5_1_3</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -30277,7 +30277,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>4_1_4</t>
+          <t>4_1_3</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -30334,7 +30334,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>3_4_10</t>
+          <t>3_4_7</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -30448,7 +30448,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>5_1_8</t>
+          <t>5_1_2</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -30562,7 +30562,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>5_3_11</t>
+          <t>5_3_9</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -30847,7 +30847,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>5_3_14</t>
+          <t>5_3_7</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -31075,7 +31075,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>3_4_8</t>
+          <t>3_4_7</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -31189,7 +31189,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>4_2_9</t>
+          <t>4_2_4</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -31303,7 +31303,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>4_2_14</t>
+          <t>4_2_9</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -31417,7 +31417,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>4_1_6</t>
+          <t>4_1_1</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -31531,7 +31531,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>3_3_7</t>
+          <t>3_3_5</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -31645,7 +31645,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>5_3_10</t>
+          <t>5_3_7</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -31702,7 +31702,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>3_6_18</t>
+          <t>3_6_15</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -31759,7 +31759,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>4_2_10</t>
+          <t>4_2_7</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -31930,7 +31930,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>3_5_17</t>
+          <t>3_5_12</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -31987,7 +31987,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>4_2_11</t>
+          <t>4_2_10</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -32101,7 +32101,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>4_2_9</t>
+          <t>4_2_7</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -32158,7 +32158,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>4_1_6</t>
+          <t>4_1_3</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -32443,7 +32443,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>3_5_12</t>
+          <t>3_5_9</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -32500,7 +32500,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>5_2_6</t>
+          <t>5_2_5</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -32557,7 +32557,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>3_5_17</t>
+          <t>3_5_10</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -32614,7 +32614,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>4_2_13</t>
+          <t>4_2_8</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -32671,7 +32671,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>5_3_13</t>
+          <t>5_3_12</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -32728,7 +32728,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>3_5_20</t>
+          <t>3_5_13</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -32842,7 +32842,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>4_2_10</t>
+          <t>4_2_8</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -33070,7 +33070,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>4_2_17</t>
+          <t>4_2_10</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -33127,7 +33127,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>3_6_15</t>
+          <t>3_6_14</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -33184,7 +33184,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>3_5_12</t>
+          <t>3_5_10</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -33298,7 +33298,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>5_3_12</t>
+          <t>5_3_11</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -33640,7 +33640,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>5_1_5</t>
+          <t>5_1_3</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -33697,7 +33697,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>4_2_15</t>
+          <t>4_2_12</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -33754,7 +33754,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>4_2_16</t>
+          <t>4_2_9</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -33868,7 +33868,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>4_1_3</t>
+          <t>4_1_1</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -33925,7 +33925,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>5_3_10</t>
+          <t>5_3_8</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -33982,7 +33982,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>3_5_14</t>
+          <t>3_5_11</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -34039,7 +34039,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>3_6_17</t>
+          <t>3_6_14</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -34267,7 +34267,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>5_2_7</t>
+          <t>5_2_5</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -34324,7 +34324,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>5_1_4</t>
+          <t>5_1_2</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -34381,7 +34381,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>5_1_6</t>
+          <t>5_1_3</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -34438,7 +34438,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>3_4_15</t>
+          <t>3_4_8</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -34609,7 +34609,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>4_2_15</t>
+          <t>4_2_10</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -34666,7 +34666,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>4_2_8</t>
+          <t>4_2_7</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -34837,7 +34837,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>5_3_11</t>
+          <t>5_3_8</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -35122,7 +35122,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>4_1_5</t>
+          <t>4_1_2</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -35236,7 +35236,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>4_1_2</t>
+          <t>4_1_1</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -35350,7 +35350,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>4_2_6</t>
+          <t>4_2_4</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -35407,7 +35407,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>4_2_9</t>
+          <t>4_2_8</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -35521,7 +35521,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>5_3_9</t>
+          <t>5_3_7</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -35635,7 +35635,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>4_2_14</t>
+          <t>4_2_7</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -35749,7 +35749,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>4_2_12</t>
+          <t>4_2_8</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -35977,7 +35977,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>4_2_11</t>
+          <t>4_2_8</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -36148,7 +36148,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>5_2_7</t>
+          <t>5_2_4</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -36205,7 +36205,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>4_2_10</t>
+          <t>4_2_9</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -36262,7 +36262,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>3_5_13</t>
+          <t>3_5_10</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -36376,7 +36376,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>4_1_3</t>
+          <t>4_1_2</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -36661,7 +36661,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>3_5_11</t>
+          <t>3_5_10</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -36718,7 +36718,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>4_2_5</t>
+          <t>4_2_4</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
@@ -36775,7 +36775,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>5_3_14</t>
+          <t>5_3_11</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -36889,7 +36889,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>4_2_7</t>
+          <t>4_2_6</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -37003,7 +37003,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>4_2_8</t>
+          <t>4_2_6</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -37060,7 +37060,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>4_2_13</t>
+          <t>4_2_12</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -37117,7 +37117,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>4_2_13</t>
+          <t>4_2_11</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -37174,7 +37174,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>3_6_16</t>
+          <t>3_6_15</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -37288,7 +37288,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>5_2_5</t>
+          <t>5_2_4</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
@@ -37402,7 +37402,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>4_2_12</t>
+          <t>4_2_11</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
@@ -37459,7 +37459,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>3_5_14</t>
+          <t>3_5_12</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
@@ -37687,7 +37687,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>4_2_12</t>
+          <t>4_2_10</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
@@ -37801,7 +37801,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>4_1_4</t>
+          <t>4_1_1</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
@@ -37915,7 +37915,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>3_3_6</t>
+          <t>3_3_3</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
@@ -38086,7 +38086,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>5_3_15</t>
+          <t>5_3_12</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
@@ -38200,7 +38200,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>4_2_14</t>
+          <t>4_2_11</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
@@ -38428,7 +38428,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>3_4_9</t>
+          <t>3_4_8</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
@@ -38485,7 +38485,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>5_2_8</t>
+          <t>5_2_5</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
@@ -38542,7 +38542,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>5_3_11</t>
+          <t>5_3_10</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
@@ -38599,7 +38599,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>3_5_13</t>
+          <t>3_5_12</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
@@ -38713,7 +38713,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>3_6_17</t>
+          <t>3_6_15</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
@@ -38827,7 +38827,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>4_2_13</t>
+          <t>4_2_10</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
@@ -38884,7 +38884,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>3_5_14</t>
+          <t>3_5_13</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
@@ -39055,7 +39055,7 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>4_2_11</t>
+          <t>4_2_9</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
@@ -39169,7 +39169,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>3_4_10</t>
+          <t>3_4_8</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
@@ -39454,7 +39454,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>4_1_4</t>
+          <t>4_1_2</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
@@ -39625,7 +39625,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>5_3_12</t>
+          <t>5_3_10</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
@@ -39682,7 +39682,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>5_2_6</t>
+          <t>5_2_4</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
@@ -39739,7 +39739,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>5_3_13</t>
+          <t>5_3_7</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
@@ -39853,7 +39853,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>5_3_12</t>
+          <t>5_3_9</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
@@ -39910,7 +39910,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>5_2_8</t>
+          <t>5_2_6</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
@@ -39967,7 +39967,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>3_5_11</t>
+          <t>3_5_9</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
@@ -40024,7 +40024,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>5_3_9</t>
+          <t>5_3_8</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
@@ -40138,7 +40138,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>3_5_15</t>
+          <t>3_5_12</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
@@ -40195,7 +40195,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>5_1_5</t>
+          <t>5_1_2</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
@@ -40309,7 +40309,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>3_3_5</t>
+          <t>3_3_3</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
@@ -40366,7 +40366,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>3_5_15</t>
+          <t>3_5_13</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
@@ -40537,7 +40537,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>5_3_13</t>
+          <t>5_3_11</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
@@ -40651,7 +40651,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>3_3_4</t>
+          <t>3_3_3</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
@@ -40879,7 +40879,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>5_3_10</t>
+          <t>5_3_9</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
@@ -40936,7 +40936,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>4_2_8</t>
+          <t>4_2_5</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
@@ -41107,7 +41107,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>3_4_7</t>
+          <t>3_4_6</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
@@ -41164,7 +41164,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>4_2_12</t>
+          <t>4_2_9</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
@@ -41449,7 +41449,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>3_4_11</t>
+          <t>3_4_8</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
@@ -41506,7 +41506,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>4_2_7</t>
+          <t>4_2_5</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
@@ -41563,7 +41563,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>3_4_8</t>
+          <t>3_4_6</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
@@ -41677,7 +41677,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>3_3_8</t>
+          <t>3_3_5</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
